--- a/data/Input.xlsx
+++ b/data/Input.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S208"/>
+  <dimension ref="A1:S218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6438,9 +6438,6 @@
       <c r="G99" t="n">
         <v>11.64</v>
       </c>
-      <c r="H99" t="n">
-        <v>13.43</v>
-      </c>
       <c r="I99" t="n">
         <v>11.4</v>
       </c>
@@ -12259,6 +12256,9 @@
           <t>tonnes per person</t>
         </is>
       </c>
+      <c r="E198" t="n">
+        <v>1.22</v>
+      </c>
       <c r="F198" t="n">
         <v>1.23</v>
       </c>
@@ -12964,6 +12964,651 @@
       <c r="S208" t="inlineStr">
         <is>
           <t>City of Vancouver Open Data, Issued building permits (full file, 52,338 permits, 2017 to Oct 2026), https://opendata.vancouver.ca/explore/dataset/issued-building-permits/ ; seismic permits counted by IssueYear (14, 16, 16, 15, 15, 12, 18, 9 for 2017-2024) divided by all permits issued that year (6726, 6737, 5577, 4383, 5015, 5950, 4678, 4914). Dataset starts in 2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Households Assets</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Housing starts, all dwelling types</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Housing units started per year (CMHC, CMA)</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>28112</v>
+      </c>
+      <c r="F209" t="n">
+        <v>33244</v>
+      </c>
+      <c r="G209" t="n">
+        <v>25983</v>
+      </c>
+      <c r="H209" t="n">
+        <v>26013</v>
+      </c>
+      <c r="I209" t="n">
+        <v>22371</v>
+      </c>
+      <c r="J209" t="n">
+        <v>28141</v>
+      </c>
+      <c r="K209" t="n">
+        <v>23404</v>
+      </c>
+      <c r="L209" t="n">
+        <v>26204</v>
+      </c>
+      <c r="M209" t="n">
+        <v>27914</v>
+      </c>
+      <c r="N209" t="n">
+        <v>20863</v>
+      </c>
+      <c r="O209" t="n">
+        <v>19212</v>
+      </c>
+      <c r="P209" t="n">
+        <v>18696</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>19027</v>
+      </c>
+      <c r="R209" t="n">
+        <v>17867</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>https://www03.cmhc-schl.gc.ca/hmip-pimh/en/TableMapChart/TableMatchingCriteria?GeographyType=MetropolitanMajorArea&amp;GeographyId=2410&amp;CategoryLevel1=New%20Housing%20Construction&amp;CategoryLevel2=Starts%20%28Actual%29&amp;ColumnField=1&amp;RowField=TIMESERIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Households Assets</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Housing completions, all dwelling types</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Housing units completed per year (CMHC, CMA)</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>25614</v>
+      </c>
+      <c r="F210" t="n">
+        <v>20797</v>
+      </c>
+      <c r="G210" t="n">
+        <v>21440</v>
+      </c>
+      <c r="H210" t="n">
+        <v>25229</v>
+      </c>
+      <c r="I210" t="n">
+        <v>24039</v>
+      </c>
+      <c r="J210" t="n">
+        <v>22603</v>
+      </c>
+      <c r="K210" t="n">
+        <v>24555</v>
+      </c>
+      <c r="L210" t="n">
+        <v>21806</v>
+      </c>
+      <c r="M210" t="n">
+        <v>18148</v>
+      </c>
+      <c r="N210" t="n">
+        <v>17346</v>
+      </c>
+      <c r="O210" t="n">
+        <v>17731</v>
+      </c>
+      <c r="P210" t="n">
+        <v>18392</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>16958</v>
+      </c>
+      <c r="R210" t="n">
+        <v>12919</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>https://www03.cmhc-schl.gc.ca/hmip-pimh/en/TableMapChart/TableMatchingCriteria?GeographyType=MetropolitanMajorArea&amp;GeographyId=2410&amp;CategoryLevel1=New%20Housing%20Construction&amp;CategoryLevel2=Completions&amp;ColumnField=1&amp;RowField=TIMESERIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Registered nurses per 100,000 population</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Registered nurses employed in direct care per 100,000 population (CIHI, province)</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>674</v>
+      </c>
+      <c r="G211" t="n">
+        <v>665.3</v>
+      </c>
+      <c r="H211" t="n">
+        <v>670.9</v>
+      </c>
+      <c r="I211" t="n">
+        <v>639.7</v>
+      </c>
+      <c r="J211" t="n">
+        <v>615.8</v>
+      </c>
+      <c r="K211" t="n">
+        <v>645.1</v>
+      </c>
+      <c r="L211" t="n">
+        <v>645.5</v>
+      </c>
+      <c r="M211" t="n">
+        <v>612.5</v>
+      </c>
+      <c r="N211" t="n">
+        <v>610</v>
+      </c>
+      <c r="O211" t="n">
+        <v>616.7</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>https://www.cihi.ca/en/nursing-in-canada-2023-data-tables (file: https://www.cihi.ca/sites/default/files/document/nursing-in-canada-2014-2023-data-tables-en.xlsx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Library programs offered</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Programs offered by the city public library system per year (count)</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>6654</v>
+      </c>
+      <c r="G212" t="n">
+        <v>6871</v>
+      </c>
+      <c r="H212" t="n">
+        <v>2580</v>
+      </c>
+      <c r="I212" t="n">
+        <v>2810</v>
+      </c>
+      <c r="J212" t="n">
+        <v>8564</v>
+      </c>
+      <c r="K212" t="n">
+        <v>8884</v>
+      </c>
+      <c r="L212" t="n">
+        <v>9167</v>
+      </c>
+      <c r="M212" t="n">
+        <v>10558</v>
+      </c>
+      <c r="N212" t="n">
+        <v>9688</v>
+      </c>
+      <c r="O212" t="n">
+        <v>10449</v>
+      </c>
+      <c r="P212" t="n">
+        <v>9218</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>8677</v>
+      </c>
+      <c r="R212" t="n">
+        <v>8498</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>https://catalogue.data.gov.bc.ca/dataset/d03007d6-d6c7-44d7-b2f8-710ba9433617/resource/f4e06e52-6072-4123-b3cf-52d2f9782040/download/2002-2025-bc-public-libraries-open-data-csv-v25.0.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Library program attendance</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Attendance at library programs per year (count)</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>176138</v>
+      </c>
+      <c r="G213" t="n">
+        <v>181706</v>
+      </c>
+      <c r="H213" t="n">
+        <v>62585</v>
+      </c>
+      <c r="I213" t="n">
+        <v>65339</v>
+      </c>
+      <c r="J213" t="n">
+        <v>247774</v>
+      </c>
+      <c r="K213" t="n">
+        <v>245307</v>
+      </c>
+      <c r="L213" t="n">
+        <v>251761</v>
+      </c>
+      <c r="M213" t="n">
+        <v>291823</v>
+      </c>
+      <c r="N213" t="n">
+        <v>276617</v>
+      </c>
+      <c r="O213" t="n">
+        <v>240240</v>
+      </c>
+      <c r="P213" t="n">
+        <v>237767</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>245180</v>
+      </c>
+      <c r="R213" t="n">
+        <v>240233</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>https://catalogue.data.gov.bc.ca/dataset/d03007d6-d6c7-44d7-b2f8-710ba9433617/resource/f4e06e52-6072-4123-b3cf-52d2f9782040/download/2002-2025-bc-public-libraries-open-data-csv-v25.0.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Library public computer sessions</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Public computer sessions per year at the city library system (count)</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>599965</v>
+      </c>
+      <c r="G214" t="n">
+        <v>584957</v>
+      </c>
+      <c r="H214" t="n">
+        <v>361748</v>
+      </c>
+      <c r="I214" t="n">
+        <v>270842</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1014584</v>
+      </c>
+      <c r="K214" t="n">
+        <v>1069192</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1194171</v>
+      </c>
+      <c r="M214" t="n">
+        <v>1211195</v>
+      </c>
+      <c r="N214" t="n">
+        <v>1273476</v>
+      </c>
+      <c r="O214" t="n">
+        <v>1287640</v>
+      </c>
+      <c r="P214" t="n">
+        <v>1331464</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>1420002</v>
+      </c>
+      <c r="R214" t="n">
+        <v>1396690</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>https://catalogue.data.gov.bc.ca/dataset/d03007d6-d6c7-44d7-b2f8-710ba9433617/resource/f4e06e52-6072-4123-b3cf-52d2f9782040/download/2002-2025-bc-public-libraries-open-data-csv-v25.0.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Public emergency alert messages issued</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Alert Ready messages issued per year (count, province)</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>16</v>
+      </c>
+      <c r="F215" t="n">
+        <v>27</v>
+      </c>
+      <c r="G215" t="n">
+        <v>7</v>
+      </c>
+      <c r="H215" t="n">
+        <v>2</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>https://www.alertready.ca/alert-count/</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Scholarly works by city universities</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Works per year by the universities located in the city (OpenAlex, count)</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>18894</v>
+      </c>
+      <c r="F216" t="n">
+        <v>18810</v>
+      </c>
+      <c r="G216" t="n">
+        <v>18365</v>
+      </c>
+      <c r="H216" t="n">
+        <v>19419</v>
+      </c>
+      <c r="I216" t="n">
+        <v>18235</v>
+      </c>
+      <c r="J216" t="n">
+        <v>16721</v>
+      </c>
+      <c r="K216" t="n">
+        <v>15850</v>
+      </c>
+      <c r="L216" t="n">
+        <v>15193</v>
+      </c>
+      <c r="M216" t="n">
+        <v>14441</v>
+      </c>
+      <c r="N216" t="n">
+        <v>14297</v>
+      </c>
+      <c r="O216" t="n">
+        <v>13614</v>
+      </c>
+      <c r="P216" t="n">
+        <v>12816</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>12664</v>
+      </c>
+      <c r="R216" t="n">
+        <v>13114</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>https://api.openalex.org/works?filter=institutions.id:I141945490|I18014758,publication_year:2011-2024&amp;group_by=publication_year&amp;per-page=200</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>International co-authorship share of scholarly works</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Share of works with at least one non-Canadian affiliation (%, OpenAlex)</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>57.0022</v>
+      </c>
+      <c r="F217" t="n">
+        <v>54.9548</v>
+      </c>
+      <c r="G217" t="n">
+        <v>56.5696</v>
+      </c>
+      <c r="H217" t="n">
+        <v>53.3241</v>
+      </c>
+      <c r="I217" t="n">
+        <v>54.368</v>
+      </c>
+      <c r="J217" t="n">
+        <v>51.6058</v>
+      </c>
+      <c r="K217" t="n">
+        <v>51.0347</v>
+      </c>
+      <c r="L217" t="n">
+        <v>48.5487</v>
+      </c>
+      <c r="M217" t="n">
+        <v>49.221</v>
+      </c>
+      <c r="N217" t="n">
+        <v>48.073</v>
+      </c>
+      <c r="O217" t="n">
+        <v>46.3714</v>
+      </c>
+      <c r="P217" t="n">
+        <v>45.1155</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>43.0433</v>
+      </c>
+      <c r="R217" t="n">
+        <v>38.4703</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>https://api.openalex.org/works?filter=institutions.id:I141945490|I18014758,publication_year:2011-2024,countries_distinct_count:&gt;1&amp;group_by=publication_year&amp;per-page=200</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Post-secondary enrolment</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Post-secondary enrolment, universities and colleges (persons, province)</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>291930</v>
+      </c>
+      <c r="F218" t="n">
+        <v>297645</v>
+      </c>
+      <c r="G218" t="n">
+        <v>286071</v>
+      </c>
+      <c r="H218" t="n">
+        <v>285921</v>
+      </c>
+      <c r="I218" t="n">
+        <v>287523</v>
+      </c>
+      <c r="J218" t="n">
+        <v>297432</v>
+      </c>
+      <c r="K218" t="n">
+        <v>295320</v>
+      </c>
+      <c r="L218" t="n">
+        <v>286914</v>
+      </c>
+      <c r="M218" t="n">
+        <v>277974</v>
+      </c>
+      <c r="N218" t="n">
+        <v>273408</v>
+      </c>
+      <c r="O218" t="n">
+        <v>271272</v>
+      </c>
+      <c r="P218" t="n">
+        <v>276726</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>273093</v>
+      </c>
+      <c r="R218" t="n">
+        <v>273123</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=3710001801</t>
         </is>
       </c>
     </row>
@@ -12978,7 +13623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K208"/>
+  <dimension ref="A1:K218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13340,7 +13985,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Vancouver only: no Calgary series found</t>
+          <t>Close proxy: definitions differ</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -13357,7 +14002,7 @@
         <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K8" s="7" t="inlineStr"/>
     </row>
@@ -13382,7 +14027,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Vancouver only: no Calgary series found</t>
+          <t>Comparable: same definition, each city's source</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -13399,7 +14044,7 @@
         <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K9" s="7" t="inlineStr"/>
     </row>
@@ -13615,7 +14260,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Vancouver only: no Calgary series found</t>
+          <t>Close proxy: definitions differ</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -13632,7 +14277,7 @@
         <v>14</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K14" s="7" t="inlineStr"/>
     </row>
@@ -13783,7 +14428,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Vancouver only: no Calgary series found</t>
+          <t>Comparable: same definition, each city's source</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -13800,7 +14445,7 @@
         <v>13</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K18" s="7" t="inlineStr"/>
     </row>
@@ -16633,7 +17278,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Vancouver only: no Calgary series found</t>
+          <t>Close proxy: definitions differ</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -16650,7 +17295,7 @@
         <v>14</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K81" s="7" t="inlineStr"/>
     </row>
@@ -16931,7 +17576,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Close proxy: definitions differ</t>
+          <t>Vancouver only: no Calgary series found</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -16948,11 +17593,11 @@
         <v>13</v>
       </c>
       <c r="J88" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>Vancouver is Metro Vancouver community emissions; Calgary is City of Calgary community inventory.</t>
+          <t>Vancouver is Metro Vancouver community emissions; Calgary is City of Calgary community inventory. Calgary entry removed 22 Oct 2026 (it repeated the series of the row before).</t>
         </is>
       </c>
     </row>
@@ -16977,7 +17622,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Vancouver only: no Calgary series found</t>
+          <t>Comparable: same definition, each city's source</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -16994,7 +17639,7 @@
         <v>13</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K89" s="7" t="inlineStr"/>
     </row>
@@ -17397,7 +18042,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Vancouver only: no Calgary series found</t>
+          <t>Close proxy: definitions differ</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -17411,12 +18056,16 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>2021 value 13.43 km2 removed on 22 Oct 2026. It breaks a series that rises 0.1 km2 per year to 11.4 in 2020 and is 11.64 from 2022, and it could not be traced to a published source.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -17481,7 +18130,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Vancouver only: no Calgary series found</t>
+          <t>Close proxy: definitions differ</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -17498,7 +18147,7 @@
         <v>14</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K101" s="7" t="inlineStr"/>
     </row>
@@ -17825,7 +18474,7 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Close proxy: definitions differ</t>
+          <t>Vancouver only: no Calgary series found</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
@@ -17842,11 +18491,11 @@
         <v>14</v>
       </c>
       <c r="J109" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>Vancouver is Metro Vancouver regional rate; Calgary is City of Calgary residential diversion.</t>
+          <t>Vancouver is Metro Vancouver regional rate; Calgary is City of Calgary residential diversion. Calgary entry removed 22 Oct 2026 (it repeated the series of the row before).</t>
         </is>
       </c>
     </row>
@@ -19817,7 +20466,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Vancouver only: no Calgary series found</t>
+          <t>Close proxy: definitions differ</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
@@ -19834,7 +20483,7 @@
         <v>12</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K153" s="7" t="inlineStr"/>
     </row>
@@ -21874,7 +22523,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J198" t="n">
         <v>14</v>
@@ -21990,7 +22639,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Vancouver only: no Calgary series found</t>
+          <t>Comparable: same definition, each city's source</t>
         </is>
       </c>
       <c r="F201" s="7" t="inlineStr">
@@ -22007,7 +22656,7 @@
         <v>14</v>
       </c>
       <c r="J201" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K201" s="7" t="inlineStr"/>
     </row>
@@ -22314,6 +22963,516 @@
         <v>0</v>
       </c>
       <c r="K208" s="7" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Households Assets</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Housing starts, all dwelling types</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Harmonised: same source and formula</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Housing units started per year (CMHC, CMA)</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://www03.cmhc-schl.gc.ca/hmip-pimh/en/TableMapChart/TableMatchingCriteria?GeographyType=MetropolitanMajorArea&amp;GeographyId=2410&amp;CategoryLevel1=New%20Housing%20Construction&amp;CategoryLevel2=Starts%20%28Actual%29&amp;ColumnField=1&amp;RowField=TIMESERIES</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>14</v>
+      </c>
+      <c r="J209" t="n">
+        <v>14</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Added in the consolidated run; see data_additions/collected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Households Assets</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Housing completions, all dwelling types</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Harmonised: same source and formula</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Housing units completed per year (CMHC, CMA)</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://www03.cmhc-schl.gc.ca/hmip-pimh/en/TableMapChart/TableMatchingCriteria?GeographyType=MetropolitanMajorArea&amp;GeographyId=2410&amp;CategoryLevel1=New%20Housing%20Construction&amp;CategoryLevel2=Completions&amp;ColumnField=1&amp;RowField=TIMESERIES</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>14</v>
+      </c>
+      <c r="J210" t="n">
+        <v>14</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Added in the consolidated run; see data_additions/collected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Registered nurses per 100,000 population</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Comparable: same definition, each city's source</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Registered nurses employed in direct care per 100,000 population (CIHI, province)</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://www.cihi.ca/en/nursing-in-canada-2023-data-tables (file: https://www.cihi.ca/sites/default/files/document/nursing-in-canada-2014-2023-data-tables-en.xlsx)</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>10</v>
+      </c>
+      <c r="J211" t="n">
+        <v>10</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Added in the consolidated run; see data_additions/collected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Library programs offered</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Close proxy: definitions differ</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Programs offered by the city public library system per year (count)</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>City library system</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://catalogue.data.gov.bc.ca/dataset/d03007d6-d6c7-44d7-b2f8-710ba9433617/resource/f4e06e52-6072-4123-b3cf-52d2f9782040/download/2002-2025-bc-public-libraries-open-data-csv-v25.0.csv</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>13</v>
+      </c>
+      <c r="J212" t="n">
+        <v>12</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Added in the consolidated run; see data_additions/collected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Library program attendance</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Close proxy: definitions differ</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Attendance at library programs per year (count)</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>City library system</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://catalogue.data.gov.bc.ca/dataset/d03007d6-d6c7-44d7-b2f8-710ba9433617/resource/f4e06e52-6072-4123-b3cf-52d2f9782040/download/2002-2025-bc-public-libraries-open-data-csv-v25.0.csv</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>13</v>
+      </c>
+      <c r="J213" t="n">
+        <v>12</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Added in the consolidated run; see data_additions/collected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Library public computer sessions</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Close proxy: definitions differ</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Public computer sessions per year at the city library system (count)</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>City library system</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://catalogue.data.gov.bc.ca/dataset/d03007d6-d6c7-44d7-b2f8-710ba9433617/resource/f4e06e52-6072-4123-b3cf-52d2f9782040/download/2002-2025-bc-public-libraries-open-data-csv-v25.0.csv</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>13</v>
+      </c>
+      <c r="J214" t="n">
+        <v>12</v>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Added in the consolidated run; see data_additions/collected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Public emergency alert messages issued</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Harmonised: same source and formula</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Alert Ready messages issued per year (count, province)</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://www.alertready.ca/alert-count/</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>6</v>
+      </c>
+      <c r="J215" t="n">
+        <v>6</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Added in the consolidated run; see data_additions/collected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Scholarly works by city universities</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Harmonised: same source and formula</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Works per year by the universities located in the city (OpenAlex, count)</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>City universities</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://api.openalex.org/works?filter=institutions.id:I141945490|I18014758,publication_year:2011-2024&amp;group_by=publication_year&amp;per-page=200</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>14</v>
+      </c>
+      <c r="J216" t="n">
+        <v>14</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Added in the consolidated run; see data_additions/collected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>International co-authorship share of scholarly works</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Harmonised: same source and formula</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Share of works with at least one non-Canadian affiliation (%, OpenAlex)</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>City universities</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://api.openalex.org/works?filter=institutions.id:I141945490|I18014758,publication_year:2011-2024,countries_distinct_count:&gt;1&amp;group_by=publication_year&amp;per-page=200</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>14</v>
+      </c>
+      <c r="J217" t="n">
+        <v>14</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Added in the consolidated run; see data_additions/collected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Knowledge Dissemination and Management</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Post-secondary enrolment</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Harmonised: same source and formula</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Post-secondary enrolment, universities and colleges (persons, province)</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=3710001801</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>14</v>
+      </c>
+      <c r="J218" t="n">
+        <v>14</v>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Added in the consolidated run; see data_additions/collected.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22326,7 +23485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22353,7 +23512,7 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>Sheet1 has the same 207 rows, order and columns as the pipeline input (years 2024 to 2011). Row k is the same sub-indicator in both files.</t>
+          <t>Sheet1 has 217 rows, years 2024 to 2011. Rows 1 to 207 are the 207 rows of the original harmonised dataset in the original order; rows 208 to 217 are the extension rows. Row k is the same sub-indicator in both files.</t>
         </is>
       </c>
     </row>
@@ -22389,7 +23548,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Related measures whose definitions still differ; see the Note column.</t>
+          <t>Related measures whose definitions still differ; see the Note column. The extension adds the library series (programs, attendance, computer sessions) with this status.</t>
         </is>
       </c>
     </row>
@@ -22413,7 +23572,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>No Calgary series yet; Calgary cells are empty.</t>
+          <t>No Calgary series yet; Calgary cells are empty. Calgary cells of ten of these rows were filled in the extension (see Extension).</t>
         </is>
       </c>
     </row>
@@ -22437,7 +23596,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Calendar year; July-to-June migration estimates labelled by end year; academic years by start year; three-year life expectancy as published by StatCan.</t>
+          <t>Calendar year; July-to-June migration estimates labelled by end year; academic years by start year; three-year life expectancy as published by StatCan. Extension: the BC public library survey year is labelled by the calendar year it describes (survey year minus one), as in rows 192 to 195.</t>
         </is>
       </c>
     </row>
@@ -22450,6 +23609,42 @@
       <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Statistics Canada values were retrieved through the Statistics Canada Web Data Service in October 2026; the Source column gives the table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Version of 2026-10-22. Original values were not changed. Ten rows were added (housing starts and completions, registered nurses per 100,000, library programs, program attendance and public computer sessions, emergency alert messages, university research output and its international co-authorship share, post-secondary enrolment). Empty cells were filled in eleven existing rows (Calgary rows 7, 8, 13, 17, 80, 88, 98, 100, 152, 200 and Vancouver row 197, year 2024). Sources, retrieval dates and comparability are in additions/additions_long.csv; the original files are in original_inputs/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Not included</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Series that could not be read from Statistics Canada tables during collection (the site was unavailable); see additions/collected/*_status.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Corrections 22 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vancouver, row 98: 2021 urban green space (13.43 km2) removed as an untraceable outlier. Calgary, rows 87 and 108: duplicate entries of rows 86 and 106 removed. These two rows now count as Vancouver only.</t>
         </is>
       </c>
     </row>
